--- a/Data/OddOneOut.xlsx
+++ b/Data/OddOneOut.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -472,87 +472,87 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which of the following does not belong to the group?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Airplane</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is not a carnivore  </t>
+          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -561,82 +561,82 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no corners, others have corners  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -646,113 +646,113 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>Eraser</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Notebook</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>Pencil</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Eraser</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Notebook</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Notebook</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shark is a fish, others are birds  </t>
+          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>53</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
+          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>97</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -761,238 +761,238 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
+          <t xml:space="preserve">Apple is fruit  </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brazil is not in Europe  </t>
+          <t xml:space="preserve">Mushroom is fungus  </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
+          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
+          <t xml:space="preserve">Cactus is succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hexagon</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1001,38 +1001,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Corn</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black is not a primary color  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1041,198 +1041,198 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
+          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Sheep</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan is an island nation  </t>
+          <t xml:space="preserve">Tiger is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>Nitrogen</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Submarine</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
+          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Aluminum</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which of these is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
+          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1241,718 +1241,718 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>July</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>July</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
+          <t xml:space="preserve">July is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>52</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which one is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ink</t>
+          <t>Hippo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Jupiter is a gas giant  </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
+          <t>Mercury</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Venus</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>Earth</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Mars</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Jupiter</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite, others planets  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid, others insects  </t>
+          <t xml:space="preserve">Hyena is not feline  </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>96</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Book is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Beetroot</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
+          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>89</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ostrich is flightless bird  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron is a ferrous metal  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Parallelogram</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Japan is an island nation  </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
           <t>Diamond</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Ruby</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Emerald</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is metal, others gemstones  </t>
+          <t xml:space="preserve">Diamond is a non-metal  </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canada is not in Europe  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Crocodile</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others planets  </t>
+          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1961,38 +1961,38 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Airplane</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
+          <t xml:space="preserve">Moon is a satellite, others are planets  </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2001,697 +2001,697 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Pine</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Oak</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not a feline  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Volleyball</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Chess is not a physical sport  </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Circle has no corners, others have corners  </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Emerald</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Silver is metal, others gemstones  </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ship</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Submarine</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
+          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is vegetable  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Hexagon</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>January</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>January</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">January is month, others days  </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">January is month, others days  </t>
+          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Parallelogram</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite, others are planets  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Guitar</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Piano</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Hippo</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Drums</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
+          <t xml:space="preserve">Flute is a wind instrument  </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
+          <t xml:space="preserve">Iron is a ferrous metal  </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennis is played individually mostly  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2701,62 +2701,62 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Hockey</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
+          <t xml:space="preserve">Tennis is played individually mostly  </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2771,28 +2771,28 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wolf is not a feline  </t>
+          <t xml:space="preserve">Hyena is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2801,232 +2801,232 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone  </t>
+          <t xml:space="preserve">Black is not a primary color  </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kathmandu is in Nepal  </t>
+          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>Circle</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Square</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>Triangle</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Square</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>Pentagon</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pepper</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rice is a grain, others condiments  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ganges</t>
+          <t>Pentagon</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Honey is not a dairy product  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -3081,38 +3081,38 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>Copper</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3121,432 +3121,432 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Crocodile</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mushroom is fungus  </t>
+          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Pine</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>Oak</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Bamboo</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chess is not a physical sport  </t>
+          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Pepper</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupiter is a gas giant  </t>
+          <t xml:space="preserve">Rice is a grain, others condiments  </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>June</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>June</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
+          <t xml:space="preserve">June is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which of the following does not belong to the group?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antarctica has no permanent residents  </t>
+          <t xml:space="preserve">Elephant is not a carnivore  </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a non-metal  </t>
+          <t xml:space="preserve">China is largest country by area  </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">June is a month, others weekdays  </t>
+          <t xml:space="preserve">Moon is a satellite  </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Canada is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Ganges</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sheep</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is wild animal  </t>
+          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
         </is>
       </c>
     </row>
@@ -3592,127 +3592,127 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Guitar</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Piano</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Drums</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flute is a wind instrument  </t>
+          <t xml:space="preserve">Sun is a star, others planets  </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>9</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Brazil is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Moon is satellite, others planets  </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -3721,278 +3721,278 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">July is a month, others weekdays  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
+          <t xml:space="preserve">Carrot is vegetable  </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which of these is odd one out?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Kathmandu is in Nepal  </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which one is odd one out?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Ink</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">China is largest country by area  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -4001,78 +4001,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Beetroot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>8</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4081,392 +4081,392 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite  </t>
+          <t xml:space="preserve">Ostrich is flightless bird  </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Spider is arachnid, others insects  </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Honey is not a dairy product  </t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Moon is satellite  </t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book is not a writing tool  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apple is fruit  </t>
+          <t xml:space="preserve">Wolf is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not feline  </t>
+          <t xml:space="preserve">Diamond is a gemstone  </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Antarctica has no permanent residents  </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is succulent plant  </t>
+          <t xml:space="preserve">Shark is a fish, others are birds  </t>
         </is>
       </c>
     </row>

--- a/Data/OddOneOut.xlsx
+++ b/Data/OddOneOut.xlsx
@@ -472,411 +472,411 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Shark is a fish, others are birds  </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Airplane</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
+          <t xml:space="preserve">Antarctica has no permanent residents  </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>Diamond</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>Copper</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Plastic</t>
-        </is>
-      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Diamond is a gemstone  </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Wolf is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
+          <t xml:space="preserve">Moon is satellite  </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apple is fruit  </t>
+          <t xml:space="preserve">Honey is not a dairy product  </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mushroom is fungus  </t>
+          <t xml:space="preserve">Spider is arachnid, others insects  </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
+          <t xml:space="preserve">Ostrich is flightless bird  </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -896,183 +896,183 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is succulent plant  </t>
+          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Beetroot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
+          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which one is odd one out?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Ink</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Kathmandu is in Nepal  </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which of these is odd one out?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
+          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1081,198 +1081,198 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sheep</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is wild animal  </t>
+          <t xml:space="preserve">Carrot is vegetable  </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
+          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">July is a month, others weekdays  </t>
+          <t xml:space="preserve">Moon is satellite, others planets  </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1281,42 +1281,42 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hippo</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
+          <t xml:space="preserve">Brazil is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1331,32 +1331,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupiter is a gas giant  </t>
+          <t xml:space="preserve">Sun is a star, others planets  </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1376,263 +1376,263 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Sun is a star, others are planets  </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Ganges</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not feline  </t>
+          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96</v>
+        <v>35</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book is not a writing tool  </t>
+          <t xml:space="preserve">Canada is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
+          <t xml:space="preserve">Moon is a satellite  </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">China is largest country by area  </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>94</v>
+        <v>2</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which of the following does not belong to the group?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Elephant is not a carnivore  </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>99</v>
+        <v>43</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1641,78 +1641,78 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>June</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>June</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan is an island nation  </t>
+          <t xml:space="preserve">June is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1721,78 +1721,78 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Pepper</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Rice is a grain, others condiments  </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Pine</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Oak</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Bamboo</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1801,198 +1801,198 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Crocodile</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a non-metal  </t>
+          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Dog is a mammal  </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>15</v>
+        <v>81</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Pentagon</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite, others are planets  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2001,158 +2001,158 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chess is not a physical sport  </t>
+          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no corners, others have corners  </t>
+          <t xml:space="preserve">Black is not a primary color  </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2161,78 +2161,78 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is metal, others gemstones  </t>
+          <t xml:space="preserve">Hyena is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17</v>
+        <v>54</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Submarine</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Hockey</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
+          <t xml:space="preserve">Tennis is played individually mostly  </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2241,57 +2241,57 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
+          <t>Dog</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
           <t>Cat</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
-      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2301,98 +2301,98 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
+          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>90</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hexagon</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">January is month, others days  </t>
+          <t xml:space="preserve">Iron is a ferrous metal  </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2401,118 +2401,118 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Guitar</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Piano</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Drums</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
+          <t xml:space="preserve">Flute is a wind instrument  </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Parallelogram</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Parallelogram</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>79</v>
+        <v>5</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2521,137 +2521,137 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Guitar</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Piano</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Drums</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flute is a wind instrument  </t>
+          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>January</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>January</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron is a ferrous metal  </t>
+          <t xml:space="preserve">January is month, others days  </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Hexagon</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
           <t>Dog</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2661,18 +2661,18 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
+          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>92</v>
+        <v>48</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2681,78 +2681,78 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Ship</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Submarine</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennis is played individually mostly  </t>
+          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2761,158 +2761,158 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Emerald</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not a feline  </t>
+          <t xml:space="preserve">Silver is metal, others gemstones  </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black is not a primary color  </t>
+          <t xml:space="preserve">Circle has no corners, others have corners  </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Volleyball</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
+          <t xml:space="preserve">Chess is not a physical sport  </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2921,198 +2921,198 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Pentagon</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Moon is a satellite, others are planets  </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>81</v>
+        <v>15</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dog is a mammal  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -3121,78 +3121,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Crocodile</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
+          <t xml:space="preserve">Diamond is a non-metal  </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Pine</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Oak</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3201,78 +3201,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pepper</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rice is a grain, others condiments  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">June is a month, others weekdays  </t>
+          <t xml:space="preserve">Japan is an island nation  </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>43</v>
+        <v>99</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3281,282 +3281,282 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2</v>
+        <v>94</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of the following does not belong to the group?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is not a carnivore  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">China is largest country by area  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite  </t>
+          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canada is not in Europe  </t>
+          <t xml:space="preserve">Book is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>63</v>
+        <v>98</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ganges</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
+          <t xml:space="preserve">Hyena is not feline  </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>3</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3576,27 +3576,27 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others are planets  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>37</v>
+        <v>69</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3611,28 +3611,28 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others planets  </t>
+          <t xml:space="preserve">Jupiter is a gas giant  </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>9</v>
+        <v>52</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3641,198 +3641,198 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hippo</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brazil is not in Europe  </t>
+          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>July</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>July</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite, others planets  </t>
+          <t xml:space="preserve">July is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
+          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Aluminum</t>
+          <t>Nitrogen</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -3841,202 +3841,202 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Sheep</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is vegetable  </t>
+          <t xml:space="preserve">Tiger is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>19</v>
+        <v>85</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which of these is odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
+          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Corn</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kathmandu is in Nepal  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which one is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ink</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Beetroot</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
+          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4046,7 +4046,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4056,417 +4056,417 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
+          <t xml:space="preserve">Cactus is succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Parrot</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
           <t>Sparrow</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>Eagle</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Ostrich</t>
-        </is>
-      </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ostrich is flightless bird  </t>
+          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid, others insects  </t>
+          <t xml:space="preserve">Mushroom is fungus  </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Honey is not a dairy product  </t>
+          <t xml:space="preserve">Apple is fruit  </t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite  </t>
+          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wolf is not a feline  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Diamond</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Airplane</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antarctica has no permanent residents  </t>
+          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shark is a fish, others are birds  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>

--- a/Data/OddOneOut.xlsx
+++ b/Data/OddOneOut.xlsx
@@ -472,207 +472,207 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shark is a fish, others are birds  </t>
+          <t xml:space="preserve">Wolf is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antarctica has no permanent residents  </t>
+          <t xml:space="preserve">Carrot is vegetable  </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wolf is not a feline  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which of the following does not belong to the group?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Elephant is not a carnivore  </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -681,64 +681,64 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>June</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>June</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">June is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Jupiter</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Moon</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Earth</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mars</t>
-        </is>
-      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Moon</t>
@@ -746,173 +746,173 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite  </t>
+          <t xml:space="preserve">Moon is satellite, others planets  </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>64</v>
+        <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Honey is not a dairy product  </t>
+          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid, others insects  </t>
+          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ostrich is flightless bird  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
+          <t xml:space="preserve">Dog is a mammal  </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -921,278 +921,278 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Hippo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beetroot</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
+          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>21</v>
+        <v>88</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which one is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ink</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">China is largest country by area  </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kathmandu is in Nepal  </t>
+          <t xml:space="preserve">Diamond is a gemstone  </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>19</v>
+        <v>62</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which of these is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Pepper</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
+          <t xml:space="preserve">Rice is a grain, others condiments  </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is vegetable  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Aluminum</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Moon is a satellite, others are planets  </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1201,118 +1201,118 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite, others planets  </t>
+          <t xml:space="preserve">Iron is a ferrous metal  </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brazil is not in Europe  </t>
+          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1321,158 +1321,158 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others planets  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which of these is odd one out?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others are planets  </t>
+          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ganges</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>66</v>
+        <v>86</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Iron</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1481,318 +1481,318 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canada is not in Europe  </t>
+          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Parallelogram</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">China is largest country by area  </t>
+          <t xml:space="preserve">Moon is satellite  </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which of the following does not belong to the group?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is not a carnivore  </t>
+          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Guitar</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Piano</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Drums</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">June is a month, others weekdays  </t>
+          <t xml:space="preserve">Flute is a wind instrument  </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pepper</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rice is a grain, others condiments  </t>
+          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pine</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Oak</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
+          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1801,38 +1801,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crocodile</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
+          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1841,158 +1841,158 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Canada is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>65</v>
+        <v>92</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dog is a mammal  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>81</v>
+        <v>14</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Black is not a primary color  </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Pentagon</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2001,238 +2001,238 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Japan is an island nation  </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1</v>
+        <v>99</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black is not a primary color  </t>
+          <t xml:space="preserve">Circle has no corners, others have corners  </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not a feline  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennis is played individually mostly  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>92</v>
+        <v>67</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2241,78 +2241,78 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Mushroom is fungus  </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
+          <t xml:space="preserve">Cactus is succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2331,188 +2331,188 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Hyena is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which one is odd one out?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Ink</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron is a ferrous metal  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Guitar</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Piano</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Drums</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flute is a wind instrument  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Parallelogram</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Antarctica has no permanent residents  </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2521,42 +2521,42 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
+          <t xml:space="preserve">Moon is a satellite  </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>49</v>
+        <v>84</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2571,124 +2571,124 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>July</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>July</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">January is month, others days  </t>
+          <t xml:space="preserve">July is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Hexagon</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Sheep</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Tiger is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
+          <t xml:space="preserve">Kathmandu is in Nepal  </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>Dog</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>Cat</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Dog</t>
-        </is>
-      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>Rabbit</t>
@@ -2696,227 +2696,227 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Submarine</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Hockey</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is metal, others gemstones  </t>
+          <t xml:space="preserve">Tennis is played individually mostly  </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no corners, others have corners  </t>
+          <t xml:space="preserve">Shark is a fish, others are birds  </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Beetroot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chess is not a physical sport  </t>
+          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>Corn</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>Sugar</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Barley</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2952,491 +2952,491 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Ship</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Submarine</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite, others are planets  </t>
+          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
+          <t xml:space="preserve">Spider is arachnid, others insects  </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Sun is a star, others are planets  </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a non-metal  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Apple is fruit  </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Ostrich is flightless bird  </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>16</v>
+        <v>94</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan is an island nation  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">Sun is a star, others planets  </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Crocodile</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
+          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3446,193 +3446,193 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
+          <t>Eraser</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>Notebook</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Pencil</t>
-        </is>
-      </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book is not a writing tool  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>82</v>
+        <v>34</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Emerald</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Silver is metal, others gemstones  </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Ganges</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not feline  </t>
+          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Aluminum</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Iron</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
           <t>Mercury</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Venus</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Earth</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Pluto</t>
-        </is>
-      </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupiter is a gas giant  </t>
+          <t xml:space="preserve">Honey is not a dairy product  </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>52</v>
+        <v>9</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -3641,638 +3641,638 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hippo</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
+          <t xml:space="preserve">Brazil is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Hexagon</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">July is a month, others weekdays  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>10</v>
+        <v>69</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
+          <t xml:space="preserve">Jupiter is a gas giant  </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Volleyball</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
+          <t xml:space="preserve">Chess is not a physical sport  </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Airplane</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
+          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sheep</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is wild animal  </t>
+          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
+          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Pine</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>Oak</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Bamboo</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Diamond is a non-metal  </t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>January</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>January</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
+          <t xml:space="preserve">January is month, others days  </t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is succulent plant  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mushroom is fungus  </t>
+          <t xml:space="preserve">Book is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>97</v>
+        <v>50</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apple is fruit  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
+          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
+          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -4281,162 +4281,162 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Pentagon</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Nitrogen</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Airplane</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
+          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4446,27 +4446,27 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Hyena is not feline  </t>
         </is>
       </c>
     </row>

--- a/Data/OddOneOut.xlsx
+++ b/Data/OddOneOut.xlsx
@@ -472,87 +472,87 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wolf is not a feline  </t>
+          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Orange</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Pluto</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is vegetable  </t>
+          <t xml:space="preserve">Pluto is a dwarf planet  </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>55</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -571,7 +571,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -592,287 +592,287 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Orange</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Carrot is vegetable  </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which of the following does not belong to the group?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is not a carnivore  </t>
+          <t xml:space="preserve">Circle has no corners, others have corners  </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Pentagon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>June</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">June is a month, others weekdays  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Oxygen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Nitrogen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Carbon</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite, others planets  </t>
+          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7</v>
+        <v>57</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Parrot</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
+          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Jasmine</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Saturn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -881,158 +881,158 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dog is a mammal  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rhino</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Hippo</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
+          <t xml:space="preserve">Hyena is not feline  </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>July</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>July</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">China is largest country by area  </t>
+          <t xml:space="preserve">July is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Dolphin</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Whale</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Octopus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a gemstone  </t>
+          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1041,72 +1041,72 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Salt</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Pepper</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rice is a grain, others condiments  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Japan is an island nation  </t>
         </is>
       </c>
     </row>
@@ -1152,171 +1152,171 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iron is a ferrous metal  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mango</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Kathmandu</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
+          <t xml:space="preserve">Kathmandu is in Nepal  </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1336,863 +1336,863 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of these is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Ostrich</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Ostrich is flightless bird  </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>Copper</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Iron</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
+          <t xml:space="preserve">Diamond is a gemstone  </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Parallelogram</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Bicycle</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>France</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is satellite  </t>
+          <t xml:space="preserve">Canada is not in Europe  </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Banana</t>
+          <t>Pine</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Guava</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Oak</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Bamboo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Papaya</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
+          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pluto</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pluto is a dwarf planet  </t>
+          <t xml:space="preserve">Notebook is for writing, others are stationery tools  </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Guitar</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Piano</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Drums</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Flute</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flute is a wind instrument  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saturn</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mars is a terrestrial planet, others are gas giants  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Parrot</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolphin is a mammal, others birds  </t>
+          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Nile</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Ganges</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bicycle</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Black Sea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Train runs on tracks, others on roads  </t>
+          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>58</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Canada is not in Europe  </t>
+          <t xml:space="preserve">Wolf is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Mango</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Carrot is a vegetable, others are fruits  </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Blue</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Yellow</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black is not a primary color  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>33</v>
+        <v>73</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Diamond is a non-metal  </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Aluminum</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Japan is an island nation  </t>
+          <t xml:space="preserve">Mercury is liquid metal  </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Boat</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Ship</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Submarine</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Guitar</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Piano</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rectangle</t>
+          <t>Drums</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Flute</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no corners, others have corners  </t>
+          <t xml:space="preserve">Flute is a wind instrument  </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Dolphin</t>
+          <t>Ruby</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Whale</t>
+          <t>Emerald</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Octopus</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Octopus is a mollusk, others are mammals  </t>
+          <t xml:space="preserve">Silver is metal, others gemstones  </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2201,118 +2201,118 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Dog is a mammal  </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Tulip</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Mushroom</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mushroom is fungus  </t>
+          <t xml:space="preserve">Spider is arachnid, others insects  </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sunflower</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is succulent plant  </t>
+          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2321,118 +2321,118 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Eagle</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Sparrow</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Crow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cheetah</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not a feline  </t>
+          <t xml:space="preserve">Shark is a fish, others are birds  </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which one is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ink</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Paper</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paper is not a writing tool  </t>
+          <t xml:space="preserve">Lion is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which one is odd one out?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lily</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Ink</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Daisy</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cactus</t>
+          <t>Paper</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cactus is a succulent plant  </t>
+          <t xml:space="preserve">Paper is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2441,78 +2441,78 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
+          <t xml:space="preserve">Moon is a satellite  </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Africa</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Antarctica</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antarctica has no permanent residents  </t>
+          <t xml:space="preserve">Sun is a star, others are planets  </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2521,118 +2521,118 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Moon</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Moon is a satellite  </t>
+          <t xml:space="preserve">Cricket uses bat and ball differently  </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>84</v>
+        <v>19</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which of these is odd one out?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Spring</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Summer</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Winter</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>July</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">July is a month, others weekdays  </t>
+          <t xml:space="preserve">Rain is a season? No, it is precipitation  </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cow</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Volleyball</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Sheep</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Chess</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is wild animal  </t>
+          <t xml:space="preserve">Chess is not a physical sport  </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2641,78 +2641,78 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kathmandu</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kathmandu is in Nepal  </t>
+          <t xml:space="preserve">Moon is satellite, others planets  </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Hyena</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
+          <t xml:space="preserve">Hyena is not a feline  </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2721,598 +2721,598 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Cube</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Cube is 3D shape  </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Red</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Cricket</t>
+          <t>Blue</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Yellow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Hockey</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tennis</t>
+          <t>Black</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tennis is played individually mostly  </t>
+          <t xml:space="preserve">Black is not a primary color  </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Select the odd one out.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Diamond</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shark is a fish, others are birds  </t>
+          <t xml:space="preserve">Diamond is a gemstone, others are metals  </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Butterfly</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Ant</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Beetroot</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Spider</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
+          <t xml:space="preserve">Spider is arachnid  </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">Apple is fruit  </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Corn</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Ship</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Submarine</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Car is land vehicle, others water vehicles  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Daisy</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid, others insects  </t>
+          <t xml:space="preserve">Cactus is a succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others are planets  </t>
+          <t xml:space="preserve">Cactus is succulent plant  </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rice</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Wheat</t>
+          <t>Lily</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barley</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sugar</t>
+          <t>Cactus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sugar is not a cereal crop  </t>
+          <t xml:space="preserve">Cactus is a succulent, others flowering plants  </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Rabbit</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>January</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>January</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal  </t>
+          <t xml:space="preserve">January is month, others days  </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>97</v>
+        <v>56</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Carrot</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Potato</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Tomato</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apple is fruit  </t>
+          <t xml:space="preserve">Water is not a metal  </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sparrow</t>
+          <t>Car</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Eagle</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Train</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Crow</t>
+          <t>Airplane</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ostrich</t>
+          <t>Bus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ostrich is flightless bird  </t>
+          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>June</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Plastic</t>
+          <t>June</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plastic is non-metal  </t>
+          <t xml:space="preserve">June is a month, others weekdays  </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Banana</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Guava</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Papaya</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is the only metal among them that is liquid at room temperature (actually Mercury is liquid; Silver is solid, so this question could be confusing)  </t>
+          <t xml:space="preserve">Papaya is tropical fruit, others are temperate  </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3321,52 +3321,52 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cube</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cube is 3D shape  </t>
+          <t xml:space="preserve">Sun is a star, others planets  </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>37</v>
+        <v>95</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Sun</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3376,63 +3376,63 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sun</t>
+          <t>Moon</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sun is a star, others planets  </t>
+          <t xml:space="preserve">Moon is satellite  </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Snake</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lizard</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Parallelogram</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Crocodile</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Frog</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3441,78 +3441,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Plastic</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Plastic is non-metal  </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Ruby</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Platinum</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Iron</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Silver is metal, others gemstones  </t>
+          <t xml:space="preserve">Iron is a ferrous metal  </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3521,112 +3521,112 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Nile</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ganges</t>
+          <t>Mars</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Black Sea</t>
+          <t>Jupiter</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Black Sea is a sea, others rivers  </t>
+          <t xml:space="preserve">Jupiter is a gas giant  </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Select the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Aluminum</t>
+          <t>Rhino</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Hippo</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mercury is liquid metal  </t>
+          <t xml:space="preserve">Tiger is carnivore, others herbivores  </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Butter</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cheese</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Honey</t>
+          <t>Mushroom</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Honey is not a dairy product  </t>
+          <t xml:space="preserve">Mushroom is fungus  </t>
         </is>
       </c>
     </row>
@@ -3672,407 +3672,407 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which of the following is odd one out?</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Rose</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Jasmine</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Hexagon</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Tulip</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Sunflower</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Sunflower is not typically a scented flower  </t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mars</t>
+          <t>Pepper</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Jupiter</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupiter is a gas giant  </t>
+          <t xml:space="preserve">Rice is a grain, others condiments  </t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Football</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Volleyball</t>
+          <t>Cheetah</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chess</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chess is not a physical sport  </t>
+          <t xml:space="preserve">Elephant is herbivore  </t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Which of the following does not belong to the group?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Airplane</t>
+          <t>Leopard</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bus runs on roads, others may use tracks or air  </t>
+          <t xml:space="preserve">Elephant is not a carnivore  </t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Rabbit</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
+          <t xml:space="preserve">Tiger is a wild animal, others are domestic  </t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore, others are carnivores  </t>
+          <t xml:space="preserve">Milk is dairy product  </t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pine</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Oak</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Bamboo</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rose</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rose is a flowering shrub, others trees or grass  </t>
+          <t xml:space="preserve">China is largest country by area  </t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>Corn</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Diamond</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Diamond is a non-metal  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Choose the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Cow</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Sheep</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>January</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">January is month, others days  </t>
+          <t xml:space="preserve">Tiger is wild animal  </t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Which of the following is odd one out?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Eraser</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Hexagon</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Notebook is not a writing instrument  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -4081,238 +4081,238 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iron</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Antarctica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Water is not a metal  </t>
+          <t xml:space="preserve">Antarctica has no permanent residents  </t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Which is the odd one out?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pen</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>China</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Notebook</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pencil</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Book is not a writing tool  </t>
+          <t xml:space="preserve">Nepal is landlocked, others are not  </t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which is the odd one out?</t>
+          <t>Pick the odd one out.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Coffee</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Tea</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Milk</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Milk is dairy product  </t>
+          <t xml:space="preserve">Book is not a writing tool  </t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which is odd one out?</t>
+          <t>Identify the odd one out.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Car</t>
+          <t>Pen</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Bus</t>
+          <t>Eraser</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Train</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Pencil</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Boat</t>
+          <t>Notebook</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boat is water vehicle, others land vehicles  </t>
+          <t xml:space="preserve">Notebook is not a writing instrument  </t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Find the odd one out.</t>
+          <t>Which is odd one out?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Football</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cricket</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Hockey</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Tennis</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lion is wild animal, others domestic  </t>
+          <t xml:space="preserve">Tennis is played individually mostly  </t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Triangle</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Pentagon</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Circle</t>
+          <t>Honey</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Circle has no sides  </t>
+          <t xml:space="preserve">Honey is not a dairy product  </t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -4321,118 +4321,118 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Butterfly</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Ant</t>
+          <t>Wheat</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Barley</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Spider</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Spider is arachnid  </t>
+          <t xml:space="preserve">Sugar is not a cereal crop  </t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pick the odd one out.</t>
+          <t>Choose the odd one out.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Square</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Rectangle</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Leopard</t>
+          <t>Triangle</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Circle</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elephant is herbivore  </t>
+          <t xml:space="preserve">Circle has no sides  </t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Identify the odd one out.</t>
+          <t>Find the odd one out.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Oxygen</t>
+          <t>Carrot</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Nitrogen</t>
+          <t>Potato</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Beetroot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbon</t>
+          <t>Tomato</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carbon is a non-gas at room temperature  </t>
+          <t xml:space="preserve">Tomato is a fruit, others are vegetables  </t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -4441,32 +4441,32 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Snake</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Lizard</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Crocodile</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hyena</t>
+          <t>Frog</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyena is not feline  </t>
+          <t xml:space="preserve">Frog is amphibian, others reptiles  </t>
         </is>
       </c>
     </row>
